--- a/artfynd/A 24483-2026 artfynd.xlsx
+++ b/artfynd/A 24483-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232520</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24483-2026 artfynd.xlsx
+++ b/artfynd/A 24483-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134232520</v>
       </c>
       <c r="B2" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24483-2026 artfynd.xlsx
+++ b/artfynd/A 24483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134232520</v>
+        <v>94896451</v>
       </c>
       <c r="B2" t="n">
-        <v>98056</v>
+        <v>43438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>101298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lang, 1789)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,19 +708,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sundänge, Vstm</t>
+          <t>S Malmviken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542945</v>
+        <v>542986</v>
       </c>
       <c r="R2" t="n">
-        <v>6604199</v>
+        <v>6604193</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2021-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,21 +767,239 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tina Nordberg, Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>72118878</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Malmviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>542986</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6604193</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-06-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tina Nordberg, Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134232520</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sundänge, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>542945</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6604199</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24483-2026 artfynd.xlsx
+++ b/artfynd/A 24483-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94896451</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72118878</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232520</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>